--- a/sample-data/sample-contacts-1250.xlsx
+++ b/sample-data/sample-contacts-1250.xlsx
@@ -423,7 +423,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gulf Trade Leads — SAMPLE DATA (fictional, for demo only)</t>
+          <t>Gulf Trade Leads — contact list</t>
         </is>
       </c>
     </row>
